--- a/data/portions of the week.xlsx
+++ b/data/portions of the week.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6dc2e15876673029/Documents/torah/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{33F73237-F31E-42F4-9D8F-DC6C9A40CCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA1CBD94-8A0B-4D35-92BE-3D3007CF3F0A}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{33F73237-F31E-42F4-9D8F-DC6C9A40CCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{509CEA36-CEAA-4AF5-AF8D-058AC9F75964}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>ויהי אברם</t>
   </si>
   <si>
-    <t>והשם פקד</t>
-  </si>
-  <si>
     <t>ואברהם זקן</t>
   </si>
   <si>
@@ -757,6 +754,9 @@
   </si>
   <si>
     <t>וישא יעקב</t>
+  </si>
+  <si>
+    <t>ויהוה פקד</t>
   </si>
 </sst>
 </file>
@@ -1154,10 +1154,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
@@ -1169,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1194,7 +1194,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>32</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>34</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>37</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>11</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>22</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>24</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>26</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>28</v>
@@ -1414,19 +1414,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>2</v>
@@ -1434,19 +1434,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>2</v>
@@ -1454,19 +1454,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>2</v>
@@ -1474,19 +1474,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>2</v>
@@ -1494,19 +1494,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>2</v>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>2</v>
@@ -1534,19 +1534,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>2</v>
@@ -1554,59 +1554,59 @@
     </row>
     <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>2</v>
@@ -1614,19 +1614,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>2</v>
@@ -1634,39 +1634,39 @@
     </row>
     <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>2</v>
@@ -1674,682 +1674,682 @@
     </row>
     <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="F30" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>161</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="C41" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="F43" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="F44" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="F47" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="F49" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="C50" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="F51" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="F54" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="F55" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="F56" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="F57" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="F58" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="C60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/portions of the week.xlsx
+++ b/data/portions of the week.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6dc2e15876673029/Documents/torah/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\osher\Documents\torah\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{33F73237-F31E-42F4-9D8F-DC6C9A40CCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{509CEA36-CEAA-4AF5-AF8D-058AC9F75964}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E70618-285B-40BA-BC80-B401A0844FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>ואברהם זקן</t>
   </si>
   <si>
-    <t>ואלה תולדות</t>
-  </si>
-  <si>
     <t>ויקם יעקב</t>
   </si>
   <si>
@@ -192,9 +189,6 @@
     <t>Walyusef yelidu</t>
   </si>
   <si>
-    <t>וליוסף נולדו</t>
-  </si>
-  <si>
     <t>Ve le Yosef Noldu</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
     <t>Ve Ele She:mot</t>
   </si>
   <si>
-    <t>45:8-48:2</t>
-  </si>
-  <si>
     <t>אל שדי</t>
   </si>
   <si>
@@ -757,6 +748,15 @@
   </si>
   <si>
     <t>ויהוה פקד</t>
+  </si>
+  <si>
+    <t>וליוסף ילדו</t>
+  </si>
+  <si>
+    <t>ואלה תולדת</t>
+  </si>
+  <si>
+    <t>46:8-48:2</t>
   </si>
 </sst>
 </file>
@@ -1154,10 +1154,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
@@ -1169,7 +1169,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1194,7 +1194,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>32</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>33</v>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>34</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>35</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>36</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>37</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>11</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>38</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>243</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>24</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>26</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>28</v>
@@ -1414,19 +1414,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>2</v>
@@ -1434,19 +1434,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>2</v>
@@ -1454,19 +1454,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>2</v>
@@ -1474,19 +1474,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>2</v>
@@ -1494,19 +1494,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>2</v>
@@ -1514,19 +1514,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>2</v>
@@ -1534,19 +1534,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>2</v>
@@ -1554,59 +1554,59 @@
     </row>
     <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>2</v>
@@ -1614,19 +1614,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>2</v>
@@ -1634,39 +1634,39 @@
     </row>
     <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>2</v>
@@ -1674,682 +1674,682 @@
     </row>
     <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="F43" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="F47" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="F49" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="F51" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="F52" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="F54" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="F55" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="F56" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="F57" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="F58" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
